--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="605">
   <si>
     <t>ID</t>
   </si>
@@ -1854,6 +1854,15 @@
   </si>
   <si>
     <t>AHB_TRN_010, AHB_BST_013, AHB_BST_016, AHB_BAS_007, AHB_ENV_008</t>
+  </si>
+  <si>
+    <t>ahb_sanity_seq</t>
+  </si>
+  <si>
+    <t>Directed SINGLE word pair and INCR4 word burst pair, written and read back to prove connectivity and environment bring up</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0, +NUM_ITER</t>
   </si>
 </sst>
 </file>
@@ -6337,19 +6346,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>549</v>
+        <v>602</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>550</v>
+        <v>603</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>456</v>
+      <c r="F3" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="625">
   <si>
     <t>ID</t>
   </si>
@@ -1863,6 +1863,66 @@
   </si>
   <si>
     <t>auto_gen_resp = 1, ready_delay 0, +NUM_ITER</t>
+  </si>
+  <si>
+    <t>all burst tests</t>
+  </si>
+  <si>
+    <t>HTRANS_STABLE_DURING_WAIT, C_IDLE_TO_NONSEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY_WAIT_TRANSITION, C_BUSY_TO_SEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY_WAIT_TRANSITION, C_BUSY_TO_SEQ_IN_WAIT, C_BUSY_TO_IDLE_IN_WAIT, C_BUSY_TO_NONSEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, every fourth burst pinned to the slot top</t>
+  </si>
+  <si>
+    <t>ahb_undefined_burst_seq</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, random sizes over every byte lane</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, random start offsets inside the wrap region</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, trailing_busy_cycles 1 to 3, busy_retract_in_wait</t>
+  </si>
+  <si>
+    <t>C_IDLE_TO_NONSEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>IDLE changed to NONSEQ while HREADY is low</t>
+  </si>
+  <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>C_BUSY_TO_SEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY changed to SEQ while HREADY is low</t>
+  </si>
+  <si>
+    <t>C_BUSY_TO_IDLE_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY changed to IDLE while HREADY is low in an INCR burst</t>
+  </si>
+  <si>
+    <t>C_BUSY_TO_NONSEQ_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY changed to NONSEQ while HREADY is low in an INCR burst</t>
+  </si>
+  <si>
+    <t>C_BUSY_HELD_IN_WAIT</t>
+  </si>
+  <si>
+    <t>BUSY held unchanged for the whole wait state</t>
   </si>
 </sst>
 </file>
@@ -2411,8 +2471,8 @@
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
+      <c r="J2" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2563,7 +2623,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>44</v>
+        <v>535</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>26</v>
@@ -2571,8 +2631,8 @@
       <c r="I7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>27</v>
+      <c r="J7" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2635,8 +2695,8 @@
       <c r="I9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
+      <c r="J9" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2763,8 +2823,8 @@
       <c r="I13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>27</v>
+      <c r="J13" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2891,8 +2951,8 @@
       <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="6" t="s">
-        <v>19</v>
+      <c r="J17" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3051,8 +3111,8 @@
       <c r="I22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="6" t="s">
-        <v>19</v>
+      <c r="J22" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -3115,8 +3175,8 @@
       <c r="I24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="6" t="s">
-        <v>19</v>
+      <c r="J24" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3179,8 +3239,8 @@
       <c r="I26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>27</v>
+      <c r="J26" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -3403,8 +3463,8 @@
       <c r="I33" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="6" t="s">
-        <v>19</v>
+      <c r="J33" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -3467,8 +3527,8 @@
       <c r="I35" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="6" t="s">
-        <v>19</v>
+      <c r="J35" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -3499,8 +3559,8 @@
       <c r="I36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="6" t="s">
-        <v>19</v>
+      <c r="J36" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -3531,8 +3591,8 @@
       <c r="I37" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J37" s="6" t="s">
-        <v>19</v>
+      <c r="J37" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -3563,8 +3623,8 @@
       <c r="I38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J38" s="6" t="s">
-        <v>19</v>
+      <c r="J38" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -3595,8 +3655,8 @@
       <c r="I39" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>19</v>
+      <c r="J39" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -3627,8 +3687,8 @@
       <c r="I40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="6" t="s">
-        <v>19</v>
+      <c r="J40" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3659,8 +3719,8 @@
       <c r="I41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="6" t="s">
-        <v>19</v>
+      <c r="J41" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3691,8 +3751,8 @@
       <c r="I42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="6" t="s">
-        <v>19</v>
+      <c r="J42" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3723,8 +3783,8 @@
       <c r="I43" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="6" t="s">
-        <v>19</v>
+      <c r="J43" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3755,8 +3815,8 @@
       <c r="I44" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>19</v>
+      <c r="J44" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
@@ -3787,8 +3847,8 @@
       <c r="I45" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J45" s="6" t="s">
-        <v>19</v>
+      <c r="J45" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -3814,13 +3874,13 @@
         <v>225</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>90</v>
+        <v>605</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J46" s="6" t="s">
-        <v>19</v>
+      <c r="J46" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3910,13 +3970,13 @@
         <v>239</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>90</v>
+        <v>605</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="6" t="s">
-        <v>19</v>
+      <c r="J49" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4035,7 +4095,7 @@
         <v>31</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>253</v>
+        <v>606</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>81</v>
@@ -4067,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>260</v>
+        <v>607</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>107</v>
@@ -4099,7 +4159,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>260</v>
+        <v>608</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>138</v>
@@ -4107,8 +4167,8 @@
       <c r="I55" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J55" s="6" t="s">
-        <v>19</v>
+      <c r="J55" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -4355,7 +4415,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>301</v>
+        <v>536</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>231</v>
@@ -4683,8 +4743,8 @@
       <c r="I73" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J73" s="7" t="s">
-        <v>27</v>
+      <c r="J73" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4971,8 +5031,8 @@
       <c r="I82" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="6" t="s">
-        <v>19</v>
+      <c r="J82" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -5632,7 +5692,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CEBD97-6CAB-4176-B36B-BC33A1F2BE8F}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
@@ -6280,6 +6340,106 @@
         <v>394</v>
       </c>
       <c r="F32" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>423</v>
       </c>
     </row>
@@ -6372,13 +6532,13 @@
         <v>553</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>554</v>
+        <v>611</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>456</v>
+      <c r="F4" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6392,13 +6552,13 @@
         <v>557</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>558</v>
+        <v>609</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>456</v>
+      <c r="F5" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6412,13 +6572,13 @@
         <v>561</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>562</v>
+        <v>612</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>456</v>
+      <c r="F6" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6426,19 +6586,19 @@
         <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>565</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>456</v>
+      <c r="F7" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="635">
   <si>
     <t>ID</t>
   </si>
@@ -1923,6 +1923,36 @@
   </si>
   <si>
     <t>BUSY held unchanged for the whole wait state</t>
+  </si>
+  <si>
+    <t>abort_on_error = 1, beats_done</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 0, ahb_slave_error_seq</t>
+  </si>
+  <si>
+    <t>abort_on_error = 0, beats_done</t>
+  </si>
+  <si>
+    <t>ADDR_CTRL_STABLE_DURING_WAIT, addr_change_on_error, C_ADDR_CHANGE_AFTER_ERROR</t>
+  </si>
+  <si>
+    <t>ahb_slave_error_seq unmapped region</t>
+  </si>
+  <si>
+    <t>ERROR injection on selected beats and on a whole unmapped region, exercising both the cancel and the continue policy</t>
+  </si>
+  <si>
+    <t>ahb_error_seq, ahb_slave_error_seq</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 0, abort_on_error 0 and 1, addr_change_on_error, +NUM_ITER, +ERROR_RATE</t>
+  </si>
+  <si>
+    <t>C_ADDR_CHANGE_AFTER_ERROR</t>
+  </si>
+  <si>
+    <t>Address moved while a burst was cancelled on an ERROR response</t>
   </si>
 </sst>
 </file>
@@ -3903,7 +3933,7 @@
         <v>24</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>230</v>
+        <v>625</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>231</v>
@@ -3911,8 +3941,8 @@
       <c r="I47" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J47" s="7" t="s">
-        <v>27</v>
+      <c r="J47" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3935,7 +3965,7 @@
         <v>24</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>235</v>
+        <v>627</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>231</v>
@@ -3943,8 +3973,8 @@
       <c r="I48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J48" s="7" t="s">
-        <v>27</v>
+      <c r="J48" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -4223,7 +4253,7 @@
         <v>31</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>249</v>
+        <v>628</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>231</v>
@@ -4231,8 +4261,8 @@
       <c r="I57" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>27</v>
+      <c r="J57" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4391,8 +4421,8 @@
       <c r="I62" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J62" s="6" t="s">
-        <v>19</v>
+      <c r="J62" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4423,8 +4453,8 @@
       <c r="I63" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J63" s="7" t="s">
-        <v>27</v>
+      <c r="J63" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4455,8 +4485,8 @@
       <c r="I64" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J64" s="7" t="s">
-        <v>27</v>
+      <c r="J64" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4487,8 +4517,8 @@
       <c r="I65" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J65" s="7" t="s">
-        <v>27</v>
+      <c r="J65" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -4519,8 +4549,8 @@
       <c r="I66" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J66" s="6" t="s">
-        <v>19</v>
+      <c r="J66" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4543,7 +4573,7 @@
         <v>24</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>320</v>
+        <v>629</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>231</v>
@@ -4551,8 +4581,8 @@
       <c r="I67" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="J67" s="7" t="s">
-        <v>27</v>
+      <c r="J67" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4863,7 +4893,7 @@
         <v>24</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>368</v>
+        <v>626</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>231</v>
@@ -4871,8 +4901,8 @@
       <c r="I77" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J77" s="7" t="s">
-        <v>27</v>
+      <c r="J77" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -5692,7 +5722,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CEBD97-6CAB-4176-B36B-BC33A1F2BE8F}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
@@ -6440,6 +6470,26 @@
         <v>495</v>
       </c>
       <c r="F37" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>423</v>
       </c>
     </row>
@@ -6646,19 +6696,19 @@
         <v>231</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>576</v>
+        <v>631</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>577</v>
+        <v>630</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>578</v>
+        <v>632</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>456</v>
+      <c r="F10" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="639">
   <si>
     <t>ID</t>
   </si>
@@ -1953,6 +1953,18 @@
   </si>
   <si>
     <t>Address moved while a burst was cancelled on an ERROR response</t>
+  </si>
+  <si>
+    <t>The slave drives HREADYOUT high for the reset period, from one clock after the assertion</t>
+  </si>
+  <si>
+    <t>HTRANS is IDLE while HRESETn is low, from one clock after the assertion</t>
+  </si>
+  <si>
+    <t>ahb_reset_seq</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, reset every 3rd burst 50 to 150 ns into a 16 beat burst</t>
   </si>
 </sst>
 </file>
@@ -2533,8 +2545,8 @@
       <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>27</v>
+      <c r="J3" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2565,8 +2577,8 @@
       <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>27</v>
+      <c r="J4" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2597,8 +2609,8 @@
       <c r="I5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>19</v>
+      <c r="J5" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2629,8 +2641,8 @@
       <c r="I6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>19</v>
+      <c r="J6" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2661,8 +2673,8 @@
       <c r="I7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>19</v>
+      <c r="J7" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2693,8 +2705,8 @@
       <c r="I8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>27</v>
+      <c r="J8" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -5841,7 +5853,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>491</v>
+        <v>636</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>483</v>
@@ -6301,7 +6313,7 @@
         <v>21</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>635</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>483</v>
@@ -6796,19 +6808,19 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>572</v>
+        <v>637</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>594</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>456</v>
+      <c r="F15" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="643">
   <si>
     <t>ID</t>
   </si>
@@ -1965,6 +1965,18 @@
   </si>
   <si>
     <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, reset every 3rd burst 50 to 150 ns into a 16 beat burst</t>
+  </si>
+  <si>
+    <t>BUSY_WAIT_TRANSITION, C_BUSY_TO_SEQ_IN_WAIT_FIXED</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, busy_cycles 1 to 3 before every beat, trailing_busy_cycles 0, busy_retract_in_wait, +NUM_ITER</t>
+  </si>
+  <si>
+    <t>C_BUSY_TO_SEQ_IN_WAIT_FIXED</t>
+  </si>
+  <si>
+    <t>BUSY changed to SEQ while HREADY is low in a fixed length burst</t>
   </si>
 </sst>
 </file>
@@ -3057,8 +3069,8 @@
       <c r="I19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>19</v>
+      <c r="J19" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3089,8 +3101,8 @@
       <c r="I20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="6" t="s">
-        <v>19</v>
+      <c r="J20" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3249,8 +3261,8 @@
       <c r="I25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>19</v>
+      <c r="J25" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4169,7 +4181,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>107</v>
@@ -4177,8 +4189,8 @@
       <c r="I54" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J54" s="6" t="s">
-        <v>19</v>
+      <c r="J54" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -5734,7 +5746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CEBD97-6CAB-4176-B36B-BC33A1F2BE8F}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
@@ -6502,6 +6514,26 @@
         <v>269</v>
       </c>
       <c r="F38" s="8" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>423</v>
       </c>
     </row>
@@ -6674,13 +6706,13 @@
         <v>569</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>570</v>
+        <v>640</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>456</v>
+      <c r="F8" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\ahb_lite_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55D61C5-19A9-4BBF-8AC6-3144B20D64E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE77A5F-1E1C-4D73-A952-1C09F5605814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="2" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Vplan" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="624">
   <si>
     <t>ID</t>
   </si>
@@ -182,9 +182,6 @@
     <t>The slave drives HREADYOUT high for the whole reset period</t>
   </si>
   <si>
-    <t>READYOUT_HIGH_IN_RESET (planned)</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -740,9 +737,6 @@
     <t>After an ERROR response the master cancels the remaining beats of the burst</t>
   </si>
   <si>
-    <t>abort_on_error = 1, scoreboard</t>
-  </si>
-  <si>
     <t>ahb_error_response_test</t>
   </si>
   <si>
@@ -755,9 +749,6 @@
     <t>After an ERROR response the master continues the remaining beats of the burst</t>
   </si>
   <si>
-    <t>abort_on_error = 0, scoreboard</t>
-  </si>
-  <si>
     <t>AHB_BST_016</t>
   </si>
   <si>
@@ -953,9 +944,6 @@
     <t>HRESP must be OKAY during any wait states inserted before the ERROR response starts</t>
   </si>
   <si>
-    <t>OKAY_BEFORE_ERROR (planned)</t>
-  </si>
-  <si>
     <t>AHB_RSP_005</t>
   </si>
   <si>
@@ -1010,9 +998,6 @@
     <t>An access to an unmapped address returns ERROR for NONSEQ and SEQ, and zero wait OKAY for IDLE and BUSY</t>
   </si>
   <si>
-    <t>Slave response sequence</t>
-  </si>
-  <si>
     <t>AHB_DAT_001</t>
   </si>
   <si>
@@ -1154,9 +1139,6 @@
     <t>The slave driver takes response items from its sequencer to control HREADY, HRESP and HRDATA per beat</t>
   </si>
   <si>
-    <t>auto_gen_resp = 0, ahb_slave_response</t>
-  </si>
-  <si>
     <t>AHB_ENV_004</t>
   </si>
   <si>
@@ -1523,9 +1505,6 @@
     <t>IDLE_DURING_RESET</t>
   </si>
   <si>
-    <t>HTRANS is IDLE while HRESETn is low</t>
-  </si>
-  <si>
     <t>Address and control are stable while HREADY is low, except when an INCR burst is ended out of BUSY</t>
   </si>
   <si>
@@ -1700,21 +1679,12 @@
     <t>ahb_single_seq</t>
   </si>
   <si>
-    <t>Minimal single write and read used to prove connectivity and environment bring up</t>
-  </si>
-  <si>
-    <t>Default configuration</t>
-  </si>
-  <si>
     <t>AHB_BAS_001 to AHB_BAS_003, AHB_TRN_004</t>
   </si>
   <si>
     <t>Randomized SINGLE bursts over all legal sizes, addresses and directions</t>
   </si>
   <si>
-    <t>Random sizes and addresses</t>
-  </si>
-  <si>
     <t>AHB_BST_001, AHB_TRN_007</t>
   </si>
   <si>
@@ -1724,9 +1694,6 @@
     <t>INCR4, INCR8 and INCR16 bursts over all legal sizes for both directions</t>
   </si>
   <si>
-    <t>Random sizes, addresses near 1KB boundaries</t>
-  </si>
-  <si>
     <t>AHB_BST_003 to AHB_BST_005, AHB_BST_009, AHB_BST_011, AHB_BST_012</t>
   </si>
   <si>
@@ -1736,21 +1703,12 @@
     <t>WRAP4, WRAP8 and WRAP16 bursts with start addresses inside and on the wrap boundary</t>
   </si>
   <si>
-    <t>Random sizes and wrap offsets</t>
-  </si>
-  <si>
     <t>AHB_BST_006 to AHB_BST_008, AHB_BST_010, AHB_DAT_006</t>
   </si>
   <si>
-    <t>ahb_incr_seq</t>
-  </si>
-  <si>
     <t>INCR bursts from 1 to 256 beats, including termination out of a BUSY transfer</t>
   </si>
   <si>
-    <t>trailing_busy_cycles greater than zero</t>
-  </si>
-  <si>
     <t>AHB_BST_002, AHB_TRN_009, AHB_WAI_006</t>
   </si>
   <si>
@@ -1760,9 +1718,6 @@
     <t>BUSY cycles inserted between beats of fixed length and undefined length bursts</t>
   </si>
   <si>
-    <t>busy_cycles 1 to 3</t>
-  </si>
-  <si>
     <t>AHB_TRN_002, AHB_TRN_003, AHB_TRN_008, AHB_WAI_005</t>
   </si>
   <si>
@@ -1772,21 +1727,6 @@
     <t>Slave back pressure sweeping 0 to 16 wait states on every beat</t>
   </si>
   <si>
-    <t>ready_delay_min and ready_delay_max</t>
-  </si>
-  <si>
-    <t>AHB_WAI_001 to AHB_WAI_004, AHB_BAS_005, AHB_BAS_006, AHB_DAT_001</t>
-  </si>
-  <si>
-    <t>ahb_error_seq, ahb_slave_response</t>
-  </si>
-  <si>
-    <t>ERROR injection on selected beats exercising both the cancel and the continue policy</t>
-  </si>
-  <si>
-    <t>auto_gen_resp = 0, abort_on_error 0 and 1</t>
-  </si>
-  <si>
     <t>AHB_RSP_003 to AHB_RSP_008, AHB_BST_014, AHB_BST_015, AHB_WAI_008</t>
   </si>
   <si>
@@ -1835,9 +1775,6 @@
     <t>Reset asserted at random points, including mid burst, with traffic resumed afterwards</t>
   </si>
   <si>
-    <t>Random reset timing</t>
-  </si>
-  <si>
     <t>AHB_RST_002 to AHB_RST_007</t>
   </si>
   <si>
@@ -1871,9 +1808,6 @@
     <t>HTRANS_STABLE_DURING_WAIT, C_IDLE_TO_NONSEQ_IN_WAIT</t>
   </si>
   <si>
-    <t>BUSY_WAIT_TRANSITION, C_BUSY_TO_SEQ_IN_WAIT</t>
-  </si>
-  <si>
     <t>BUSY_WAIT_TRANSITION, C_BUSY_TO_SEQ_IN_WAIT, C_BUSY_TO_IDLE_IN_WAIT, C_BUSY_TO_NONSEQ_IN_WAIT</t>
   </si>
   <si>
@@ -1977,6 +1911,15 @@
   </si>
   <si>
     <t>BUSY changed to SEQ while HREADY is low in a fixed length burst</t>
+  </si>
+  <si>
+    <t>ahb_wait_state_seq</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready delay window swept 0 to 16 at run time, en_idle_to_nonseq_in_wait = 1, +NUM_ITER, +WAIT_MAX</t>
+  </si>
+  <si>
+    <t>AHB_WAI_001 to AHB_WAI_004, AHB_WAI_009, AHB_BAS_005, AHB_BAS_006, AHB_RSP_002, AHB_DAT_001</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +2014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2115,7 +2058,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2454,7 +2396,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
     <col min="3" max="3" width="18.77734375" customWidth="1"/>
     <col min="4" max="4" width="30.77734375" style="5" customWidth="1"/>
     <col min="5" max="5" width="58.77734375" style="5" customWidth="1"/>
@@ -2526,7 +2468,7 @@
         <v>18</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2558,7 +2500,7 @@
         <v>18</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2590,7 +2532,7 @@
         <v>18</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2622,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2654,7 +2596,7 @@
         <v>18</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2677,21 +2619,21 @@
         <v>36</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>21</v>
@@ -2700,16 +2642,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>26</v>
@@ -2718,12 +2660,12 @@
         <v>18</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2">
         <v>2.1</v>
@@ -2732,115 +2674,115 @@
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2">
         <v>3.1</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <v>3.1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2">
         <v>3.1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>18</v>
@@ -2851,31 +2793,31 @@
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2">
         <v>3.1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>19</v>
@@ -2883,95 +2825,95 @@
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2">
         <v>3.1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2">
         <v>3.1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="2">
         <v>3.1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>27</v>
@@ -2979,60 +2921,60 @@
     </row>
     <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2">
         <v>2.2000000000000002</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2">
         <v>3.2</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>18</v>
@@ -3043,89 +2985,89 @@
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" s="2">
         <v>3.2</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="2">
         <v>3.2</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="2">
         <v>3.2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
@@ -3139,63 +3081,63 @@
     </row>
     <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="2">
         <v>3.2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="2">
         <v>3.2</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>19</v>
@@ -3203,124 +3145,124 @@
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B27" s="2">
         <v>3.2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="H27" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>18</v>
@@ -3331,28 +3273,28 @@
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28" s="2">
         <v>3.4</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>18</v>
@@ -3363,28 +3305,28 @@
     </row>
     <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B29" s="2">
         <v>3.4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="H29" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>18</v>
@@ -3395,60 +3337,60 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B30" s="2">
         <v>3.4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="H30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B31" s="2">
         <v>3.4</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="H31" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>18</v>
@@ -3459,28 +3401,28 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B32" s="2">
         <v>3.5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="H32" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>18</v>
@@ -3491,860 +3433,860 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2">
         <v>3.4</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B34" s="2">
         <v>3.5</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="H34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B35" s="2">
         <v>3.5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="H35" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B36" s="2">
         <v>3.5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="H36" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B37" s="2">
         <v>3.5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D37" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="H37" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B38" s="2">
         <v>3.5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="H38" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B39" s="2">
         <v>3.5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" s="2">
         <v>3.5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="H40" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" s="2">
         <v>3.5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D41" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="F41" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="H41" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B42" s="2">
         <v>3.5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B43" s="2">
         <v>3.5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="H43" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B44" s="2">
         <v>3.5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="H44" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B45" s="2">
         <v>3.5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B46" s="2">
         <v>3.5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="H46" s="4" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B49" s="2">
         <v>3.5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B50" s="2">
         <v>3.6</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>244</v>
-      </c>
       <c r="H50" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="F58" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>277</v>
-      </c>
       <c r="H58" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B59" s="2">
         <v>3.2</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>18</v>
@@ -4355,348 +4297,348 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="E60" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="F60" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="H60" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J60" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>292</v>
-      </c>
       <c r="H61" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="G65" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>311</v>
-      </c>
       <c r="H65" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B66" s="2">
         <v>5.0999999999999996</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>328</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B70" s="2">
         <v>6.1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>18</v>
@@ -4707,31 +4649,31 @@
     </row>
     <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B71" s="2">
         <v>6.1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J71" s="7" t="s">
         <v>27</v>
@@ -4739,95 +4681,95 @@
     </row>
     <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B72" s="2">
         <v>6.1</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B73" s="2">
         <v>6.1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B74" s="2">
         <v>6.2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>27</v>
@@ -4835,31 +4777,31 @@
     </row>
     <row r="75" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J75" s="7" t="s">
         <v>27</v>
@@ -4867,95 +4809,95 @@
     </row>
     <row r="76" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J78" s="7" t="s">
         <v>27</v>
@@ -4963,95 +4905,95 @@
     </row>
     <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>27</v>
@@ -5059,230 +5001,235 @@
     </row>
     <row r="82" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B84" s="2">
         <v>3.3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B85" s="2">
         <v>3.7</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>401</v>
-      </c>
       <c r="F85" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B86" s="2">
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B87" s="2">
         <v>1.3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B88" s="2">
         <v>6.2</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{1663D931-9CC1-4612-A7CC-03B6518F073A}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Complete,In Progress,Not Started,Excluded" sqref="J2:J88" xr:uid="{05FD6F0D-5805-479B-BCD2-D4F58AE3FDC6}">
+      <formula1>"Complete,In Progress,Not Started,Excluded"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5303,22 +5250,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -5326,420 +5273,425 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E2" s="10">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>424</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E18" s="10">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E19" s="10">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{AD12BF43-B967-4617-8F80-C6A521600B7B}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Implemented,Planned" sqref="G2:G19" xr:uid="{7BD80A70-0D96-4557-A8B5-398CAF7B5CD4}">
+      <formula1>"Implemented,Planned"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5759,19 +5711,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -5779,102 +5731,102 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B2" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B3" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B4" s="12">
         <v>2.2999999999999998</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5888,657 +5840,662 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B12" s="12">
         <v>3.5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B13" s="12">
         <v>3.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B14" s="12">
         <v>3.5</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="12">
         <v>3.2</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B21" s="12">
         <v>3.2</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B22" s="12">
         <v>3.5</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="B23" s="12">
         <v>3.5</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="B24" s="12">
         <v>3.5</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B27" s="12">
         <v>3.2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="12">
         <v>3.2</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B31" s="12">
         <v>3.7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B32" s="12">
         <v>3.3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>614</v>
+        <v>592</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>642</v>
+        <v>620</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{17CEBD97-6CAB-4176-B36B-BC33A1F2BE8F}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Implemented,Planned" sqref="F2:F39" xr:uid="{3450980D-0FBD-4246-B895-1D64A844B483}">
+      <formula1>"Implemented,Planned"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6560,16 +6517,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -6577,22 +6534,22 @@
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6600,239 +6557,239 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>611</v>
+        <v>589</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>572</v>
+        <v>621</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>574</v>
+        <v>622</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>456</v>
+        <v>623</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>631</v>
+        <v>609</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>632</v>
+        <v>610</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>582</v>
+        <v>562</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6840,63 +6797,68 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>637</v>
+        <v>615</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>638</v>
+        <v>616</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{A0114BF8-2CC7-4FE1-B6B2-9B2CAEF23C2C}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Implemented,Planned" sqref="F2:F17" xr:uid="{3D5BF63E-B271-4C49-9F28-D8536571196C}">
+      <formula1>"Implemented,Planned"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="629">
   <si>
     <t>ID</t>
   </si>
@@ -1920,6 +1920,21 @@
   </si>
   <si>
     <t>AHB_WAI_001 to AHB_WAI_004, AHB_WAI_009, AHB_BAS_005, AHB_BAS_006, AHB_RSP_002, AHB_DAT_001</t>
+  </si>
+  <si>
+    <t>ahb_byte_lane_seq</t>
+  </si>
+  <si>
+    <t>Byte, halfword and word transfers at every legal alignment, with a check that every HSIZE fitting the bus is accepted and every wider one rejected</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, +CHK_SIZE_ENCODINGS, sweep order shuffled per seed, burst position randomized inside each slot</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, ready_delay 0 to 2, +NUM_ITER, slot and lane order shuffled per seed, directed lane payload with the inverted payload on the inactive lanes</t>
+  </si>
+  <si>
+    <t>SIZE_MAX, c_size_max, cp_size ignore bins, ahb_size_seq encoding check</t>
   </si>
 </sst>
 </file>
@@ -3299,8 +3314,8 @@
       <c r="I28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="6" t="s">
-        <v>19</v>
+      <c r="J28" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3331,8 +3346,8 @@
       <c r="I29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="6" t="s">
-        <v>19</v>
+      <c r="J29" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -3387,7 +3402,7 @@
         <v>160</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>161</v>
+        <v>628</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>148</v>
@@ -3395,8 +3410,8 @@
       <c r="I31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="6" t="s">
-        <v>19</v>
+      <c r="J31" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -3427,8 +3442,8 @@
       <c r="I32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="6" t="s">
-        <v>19</v>
+      <c r="J32" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -4643,8 +4658,8 @@
       <c r="I70" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J70" s="7" t="s">
-        <v>27</v>
+      <c r="J70" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -4675,8 +4690,8 @@
       <c r="I71" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J71" s="7" t="s">
-        <v>27</v>
+      <c r="J71" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -6720,16 +6735,16 @@
         <v>560</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>561</v>
+        <v>625</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>562</v>
+        <v>626</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>450</v>
+      <c r="F11" s="8" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6737,19 +6752,19 @@
         <v>331</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>560</v>
+        <v>624</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>564</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>565</v>
+        <v>627</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>450</v>
+      <c r="F12" s="8" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\ahb_lite_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE77A5F-1E1C-4D73-A952-1C09F5605814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8BB20D-529B-4735-A6A5-291D7E90287F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="626">
   <si>
     <t>ID</t>
   </si>
@@ -533,9 +533,6 @@
     <t>SVA, Constraint</t>
   </si>
   <si>
-    <t>SIZE_MAX, c_size_max, cp_size ignore bins</t>
-  </si>
-  <si>
     <t>AHB_SIZ_005</t>
   </si>
   <si>
@@ -1733,21 +1730,12 @@
     <t>ahb_size_seq</t>
   </si>
   <si>
-    <t>Byte, halfword and word transfers at every legal alignment, including illegal size rejection</t>
-  </si>
-  <si>
-    <t>Random sizes and offsets</t>
-  </si>
-  <si>
     <t>AHB_SIZ_001 to AHB_SIZ_006</t>
   </si>
   <si>
     <t>Narrow transfers checked against the reference memory on every active byte lane</t>
   </si>
   <si>
-    <t>Random offsets, word aligned base</t>
-  </si>
-  <si>
     <t>AHB_DAT_003, AHB_DAT_004</t>
   </si>
   <si>
@@ -1935,13 +1923,16 @@
   </si>
   <si>
     <t>SIZE_MAX, c_size_max, cp_size ignore bins, ahb_size_seq encoding check</t>
+  </si>
+  <si>
+    <t>ahb_back_to_back_seq</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1981,6 +1972,14 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Aptos Narrow"/>
@@ -2029,7 +2028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2072,6 +2071,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2634,7 +2636,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>26</v>
@@ -3402,7 +3404,7 @@
         <v>160</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>148</v>
@@ -3416,7 +3418,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B32" s="2">
         <v>3.5</v>
@@ -3425,16 +3427,16 @@
         <v>144</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>148</v>
@@ -3448,7 +3450,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B33" s="2">
         <v>3.4</v>
@@ -3457,10 +3459,10 @@
         <v>144</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
@@ -3480,25 +3482,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B34" s="2">
         <v>3.5</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>128</v>
@@ -3512,25 +3514,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B35" s="2">
         <v>3.5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>137</v>
@@ -3544,25 +3546,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B36" s="2">
         <v>3.5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>94</v>
@@ -3576,25 +3578,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2">
         <v>3.5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D37" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>94</v>
@@ -3608,25 +3610,25 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2">
         <v>3.5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>94</v>
@@ -3640,28 +3642,28 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B39" s="2">
         <v>3.5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G39" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>18</v>
@@ -3672,28 +3674,28 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B40" s="2">
         <v>3.5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="H40" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>18</v>
@@ -3704,28 +3706,28 @@
     </row>
     <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B41" s="2">
         <v>3.5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D41" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="F41" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="H41" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>18</v>
@@ -3736,25 +3738,25 @@
     </row>
     <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" s="2">
         <v>3.5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>94</v>
@@ -3768,28 +3770,28 @@
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B43" s="2">
         <v>3.5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="H43" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>18</v>
@@ -3800,25 +3802,25 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B44" s="2">
         <v>3.5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>94</v>
@@ -3832,19 +3834,19 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B45" s="2">
         <v>3.5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
@@ -3864,28 +3866,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B46" s="2">
         <v>3.5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>18</v>
@@ -3896,28 +3898,28 @@
     </row>
     <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>18</v>
@@ -3928,28 +3930,28 @@
     </row>
     <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>44</v>
@@ -3960,28 +3962,28 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B49" s="2">
         <v>3.5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>44</v>
@@ -3992,25 +3994,25 @@
     </row>
     <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B50" s="2">
         <v>3.6</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>78</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>80</v>
@@ -4024,25 +4026,25 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>80</v>
@@ -4056,25 +4058,25 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>80</v>
@@ -4088,25 +4090,25 @@
     </row>
     <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>80</v>
@@ -4120,25 +4122,25 @@
     </row>
     <row r="54" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>106</v>
@@ -4152,25 +4154,25 @@
     </row>
     <row r="55" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>137</v>
@@ -4184,31 +4186,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>101</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>27</v>
@@ -4216,28 +4218,28 @@
     </row>
     <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>44</v>
@@ -4248,31 +4250,31 @@
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>80</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J58" s="7" t="s">
         <v>19</v>
@@ -4280,25 +4282,25 @@
     </row>
     <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B59" s="2">
         <v>3.2</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>101</v>
@@ -4312,25 +4314,25 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>61</v>
@@ -4344,25 +4346,25 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>80</v>
@@ -4376,28 +4378,28 @@
     </row>
     <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>18</v>
@@ -4408,28 +4410,28 @@
     </row>
     <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>44</v>
@@ -4440,28 +4442,28 @@
     </row>
     <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>18</v>
@@ -4472,28 +4474,28 @@
     </row>
     <row r="65" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="F65" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="G65" s="4" t="s">
-        <v>307</v>
-      </c>
       <c r="H65" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>44</v>
@@ -4504,28 +4506,28 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B66" s="2">
         <v>5.0999999999999996</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>44</v>
@@ -4536,31 +4538,31 @@
     </row>
     <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>62</v>
@@ -4568,25 +4570,25 @@
     </row>
     <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>80</v>
@@ -4600,25 +4602,25 @@
     </row>
     <row r="69" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="E69" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>61</v>
@@ -4632,28 +4634,28 @@
     </row>
     <row r="70" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B70" s="2">
         <v>6.1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>18</v>
@@ -4664,28 +4666,28 @@
     </row>
     <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B71" s="2">
         <v>6.1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>334</v>
-      </c>
       <c r="F71" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G71" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H71" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>44</v>
@@ -4696,25 +4698,25 @@
     </row>
     <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B72" s="2">
         <v>6.1</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>337</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>61</v>
@@ -4728,28 +4730,28 @@
     </row>
     <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B73" s="2">
         <v>6.1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D73" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="F73" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>18</v>
@@ -4760,31 +4762,31 @@
     </row>
     <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B74" s="2">
         <v>6.2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="H74" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="I74" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>27</v>
@@ -4792,28 +4794,28 @@
     </row>
     <row r="75" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G75" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>44</v>
@@ -4824,25 +4826,25 @@
     </row>
     <row r="76" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>61</v>
@@ -4856,28 +4858,28 @@
     </row>
     <row r="77" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D77" s="4" t="s">
+      <c r="E77" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>18</v>
@@ -4888,25 +4890,25 @@
     </row>
     <row r="78" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>70</v>
@@ -4920,25 +4922,25 @@
     </row>
     <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="F79" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>370</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>54</v>
@@ -4952,25 +4954,25 @@
     </row>
     <row r="80" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>61</v>
@@ -4984,31 +4986,31 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>27</v>
@@ -5016,25 +5018,25 @@
     </row>
     <row r="82" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="F82" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>54</v>
@@ -5048,25 +5050,25 @@
     </row>
     <row r="83" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>54</v>
@@ -5080,162 +5082,162 @@
     </row>
     <row r="84" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B84" s="2">
         <v>3.3</v>
       </c>
       <c r="C84" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="E84" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="F84" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>392</v>
-      </c>
       <c r="H84" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B85" s="2">
         <v>3.7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="F85" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>396</v>
-      </c>
       <c r="H85" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B86" s="2">
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>399</v>
-      </c>
       <c r="F86" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B87" s="2">
         <v>1.3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D87" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>402</v>
-      </c>
       <c r="F87" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B88" s="2">
         <v>6.2</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D88" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="F88" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -5265,22 +5267,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -5288,131 +5290,131 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="E2" s="10">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>416</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -5421,113 +5423,113 @@
         <v>102</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
@@ -5536,113 +5538,113 @@
         <v>138</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>453</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>460</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>467</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
@@ -5651,53 +5653,53 @@
         <v>45</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="E18" s="10">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="E19" s="10">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -5726,19 +5728,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -5746,102 +5748,102 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B2" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B3" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="12">
         <v>2.2999999999999998</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5855,73 +5857,73 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -5929,79 +5931,79 @@
         <v>84</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>81</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B12" s="12">
         <v>3.5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B13" s="12">
         <v>3.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>157</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B14" s="12">
         <v>3.5</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6009,39 +6011,39 @@
         <v>93</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>498</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>123</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -6052,36 +6054,36 @@
         <v>124</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>129</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>124</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>123</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -6092,176 +6094,176 @@
         <v>3.2</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>119</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>506</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B21" s="12">
         <v>3.2</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>102</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B22" s="12">
         <v>3.5</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>511</v>
-      </c>
       <c r="F22" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B23" s="12">
         <v>3.5</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>514</v>
-      </c>
       <c r="F23" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B24" s="12">
         <v>3.5</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>517</v>
-      </c>
       <c r="F24" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>519</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>521</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B27" s="12">
         <v>3.2</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>525</v>
-      </c>
       <c r="F27" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -6272,236 +6274,236 @@
         <v>3.2</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>527</v>
-      </c>
       <c r="F28" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>530</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B31" s="12">
         <v>3.7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B32" s="12">
         <v>3.3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -6532,16 +6534,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -6552,19 +6554,19 @@
         <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>541</v>
-      </c>
       <c r="F2" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6572,19 +6574,19 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6592,19 +6594,19 @@
         <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>545</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6612,39 +6614,39 @@
         <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>548</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>551</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6652,19 +6654,19 @@
         <v>137</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>553</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6672,19 +6674,19 @@
         <v>106</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>556</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -6692,39 +6694,39 @@
         <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6732,39 +6734,39 @@
         <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>563</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6772,19 +6774,19 @@
         <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>557</v>
+        <v>625</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>450</v>
+        <v>565</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6792,19 +6794,19 @@
         <v>101</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6812,39 +6814,39 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6852,19 +6854,19 @@
         <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/doc/ahb_lite_vplan.xlsx
+++ b/doc/ahb_lite_vplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\ahb_lite_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8BB20D-529B-4735-A6A5-291D7E90287F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A385D4B1-D580-4D06-AE29-B7FDCF8F0AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Vplan" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="629">
   <si>
     <t>ID</t>
   </si>
@@ -350,9 +350,6 @@
     <t>SVA, Coverage</t>
   </si>
   <si>
-    <t>IDLE_OKAY_RESP, cp_trans.idle (planned)</t>
-  </si>
-  <si>
     <t>ahb_idle_test</t>
   </si>
   <si>
@@ -392,9 +389,6 @@
     <t>The first beat of a burst, and any single transfer, is signalled as NONSEQ</t>
   </si>
   <si>
-    <t>c_trans_active, cp_trans.nonseq (planned)</t>
-  </si>
-  <si>
     <t>AHB_TRN_005</t>
   </si>
   <si>
@@ -476,9 +470,6 @@
     <t>Coverage</t>
   </si>
   <si>
-    <t>cp_trans (planned)</t>
-  </si>
-  <si>
     <t>AHB_SIZ_001</t>
   </si>
   <si>
@@ -1109,9 +1100,6 @@
     <t>An agent builds driver, sequencer and monitor when active, and only the monitor when passive</t>
   </si>
   <si>
-    <t>is_active</t>
-  </si>
-  <si>
     <t>ahb_passive_test</t>
   </si>
   <si>
@@ -1145,9 +1133,6 @@
     <t>The accept loop stalls once max_outstanding transactions are accepted but not yet complete</t>
   </si>
   <si>
-    <t>max_outstanding</t>
-  </si>
-  <si>
     <t>AHB_ENV_005</t>
   </si>
   <si>
@@ -1718,9 +1703,6 @@
     <t>AHB_TRN_002, AHB_TRN_003, AHB_TRN_008, AHB_WAI_005</t>
   </si>
   <si>
-    <t>ahb_random_seq</t>
-  </si>
-  <si>
     <t>Slave back pressure sweeping 0 to 16 wait states on every beat</t>
   </si>
   <si>
@@ -1751,12 +1733,6 @@
     <t>ahb_idle_seq</t>
   </si>
   <si>
-    <t>IDLE transfers between bursts, address changes during IDLE and illegal follow up checks</t>
-  </si>
-  <si>
-    <t>Random idle gaps</t>
-  </si>
-  <si>
     <t>AHB_TRN_001, AHB_TRN_006, AHB_WAI_007, AHB_WAI_010</t>
   </si>
   <si>
@@ -1766,18 +1742,6 @@
     <t>AHB_RST_002 to AHB_RST_007</t>
   </si>
   <si>
-    <t>Master agent set to passive with external stimulus while monitors and checkers stay active</t>
-  </si>
-  <si>
-    <t>is_active = UVM_PASSIVE</t>
-  </si>
-  <si>
-    <t>Long randomized run mixing every burst type, size, wait state, BUSY and error scenario</t>
-  </si>
-  <si>
-    <t>Full random, multi seed regression</t>
-  </si>
-  <si>
     <t>AHB_TRN_010, AHB_BST_013, AHB_BST_016, AHB_BAS_007, AHB_ENV_008</t>
   </si>
   <si>
@@ -1926,13 +1890,58 @@
   </si>
   <si>
     <t>ahb_back_to_back_seq</t>
+  </si>
+  <si>
+    <t>IDLE_OKAY_RESP, ahb_trans_cg.cp_trans.idle</t>
+  </si>
+  <si>
+    <t>c_trans_active, ahb_trans_cg.cp_trans.nonseq</t>
+  </si>
+  <si>
+    <t>ahb_trans_cg.cp_trans</t>
+  </si>
+  <si>
+    <t>ahb_idle_test bus watcher, num_idle_wait_addr_change</t>
+  </si>
+  <si>
+    <t>is_active, passive topology checks, num_observed</t>
+  </si>
+  <si>
+    <t>max_outstanding, deepest_per_window, limit_violations</t>
+  </si>
+  <si>
+    <t>ahb_trans_cg</t>
+  </si>
+  <si>
+    <t>Exercises accepted IDLE and BUSY cycles, legal post-IDLE transitions, and address changes while IDLE is held during a wait state</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, en_back_to_back = 1, en_idle_to_nonseq_in_wait = 1, +NUM_ITER, +MAX_GAP</t>
+  </si>
+  <si>
+    <t>ahb_passive_seq</t>
+  </si>
+  <si>
+    <t>Sets the slave agent to passive while the active master drives a deterministic SINGLE/INCR4 write matrix across 8/16/32-bit transfers; checks that the passive monitor observes every transaction</t>
+  </si>
+  <si>
+    <t>slave is_active = UVM_PASSIVE, +NUM_ITER (minimum 6)</t>
+  </si>
+  <si>
+    <t>ahb_random_stress_seq</t>
+  </si>
+  <si>
+    <t>Constrained-random write/read-back stress across all burst types and legal sizes, with back-to-back traffic, BUSY insertion, and variable wait states</t>
+  </si>
+  <si>
+    <t>auto_gen_resp = 1, en_back_to_back = 1, ready_delay = 0 to +WAIT_MAX, +NUM_ITER, +WAIT_MAX, multi-seed regression</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1972,14 +1981,6 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Aptos Narrow"/>
@@ -2028,7 +2029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2071,9 +2072,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2636,7 +2634,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>26</v>
@@ -2804,8 +2802,8 @@
       <c r="I12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="6" t="s">
-        <v>19</v>
+      <c r="J12" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2836,8 +2834,8 @@
       <c r="I13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>19</v>
+      <c r="J13" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2868,7 +2866,7 @@
       <c r="I14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="8" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2900,7 +2898,7 @@
       <c r="I15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="8" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2932,8 +2930,8 @@
       <c r="I16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>27</v>
+      <c r="J16" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2988,21 +2986,21 @@
         <v>99</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>19</v>
+      <c r="J18" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2">
         <v>3.2</v>
@@ -3011,19 +3009,19 @@
         <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>99</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>18</v>
@@ -3034,7 +3032,7 @@
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2">
         <v>3.2</v>
@@ -3043,19 +3041,19 @@
         <v>96</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>44</v>
@@ -3066,7 +3064,7 @@
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B21" s="2">
         <v>3.2</v>
@@ -3075,16 +3073,16 @@
         <v>96</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
@@ -3092,13 +3090,13 @@
       <c r="I21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>19</v>
+      <c r="J21" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B22" s="2">
         <v>3.2</v>
@@ -3107,16 +3105,16 @@
         <v>96</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>94</v>
@@ -3130,7 +3128,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2">
         <v>3.2</v>
@@ -3139,51 +3137,51 @@
         <v>96</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>19</v>
+      <c r="J23" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>44</v>
@@ -3194,28 +3192,28 @@
     </row>
     <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>18</v>
@@ -3226,28 +3224,28 @@
     </row>
     <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>44</v>
@@ -3258,7 +3256,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" s="2">
         <v>3.2</v>
@@ -3267,16 +3265,16 @@
         <v>96</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="G27" s="4" t="s">
-        <v>142</v>
+        <v>616</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>89</v>
@@ -3284,34 +3282,34 @@
       <c r="I27" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>27</v>
+      <c r="J27" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2">
         <v>3.4</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>18</v>
@@ -3322,28 +3320,28 @@
     </row>
     <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B29" s="2">
         <v>3.4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>18</v>
@@ -3354,25 +3352,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B30" s="2">
         <v>3.4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>61</v>
@@ -3386,28 +3384,28 @@
     </row>
     <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B31" s="2">
         <v>3.4</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>18</v>
@@ -3418,28 +3416,28 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B32" s="2">
         <v>3.5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>18</v>
@@ -3450,19 +3448,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2">
         <v>3.4</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
@@ -3482,28 +3480,28 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B34" s="2">
         <v>3.5</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="H34" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>18</v>
@@ -3514,28 +3512,28 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B35" s="2">
         <v>3.5</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>18</v>
@@ -3546,25 +3544,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2">
         <v>3.5</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G36" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>94</v>
@@ -3578,25 +3576,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B37" s="2">
         <v>3.5</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>94</v>
@@ -3610,25 +3608,25 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B38" s="2">
         <v>3.5</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="G38" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>94</v>
@@ -3642,28 +3640,28 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B39" s="2">
         <v>3.5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>18</v>
@@ -3674,28 +3672,28 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2">
         <v>3.5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>18</v>
@@ -3706,28 +3704,28 @@
     </row>
     <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B41" s="2">
         <v>3.5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>18</v>
@@ -3738,25 +3736,25 @@
     </row>
     <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B42" s="2">
         <v>3.5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>94</v>
@@ -3770,28 +3768,28 @@
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B43" s="2">
         <v>3.5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="H43" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>18</v>
@@ -3802,25 +3800,25 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B44" s="2">
         <v>3.5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>94</v>
@@ -3834,19 +3832,19 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B45" s="2">
         <v>3.5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
@@ -3866,28 +3864,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B46" s="2">
         <v>3.5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>18</v>
@@ -3898,28 +3896,28 @@
     </row>
     <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>18</v>
@@ -3930,28 +3928,28 @@
     </row>
     <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>44</v>
@@ -3962,28 +3960,28 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B49" s="2">
         <v>3.5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>44</v>
@@ -3994,25 +3992,25 @@
     </row>
     <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B50" s="2">
         <v>3.6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>78</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>80</v>
@@ -4020,31 +4018,31 @@
       <c r="I50" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>80</v>
@@ -4052,31 +4050,31 @@
       <c r="I51" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>80</v>
@@ -4084,31 +4082,31 @@
       <c r="I52" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>80</v>
@@ -4116,34 +4114,34 @@
       <c r="I53" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>44</v>
@@ -4154,28 +4152,28 @@
     </row>
     <row r="55" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>44</v>
@@ -4184,62 +4182,62 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>245</v>
+        <v>617</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>27</v>
+        <v>261</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>44</v>
@@ -4250,89 +4248,89 @@
     </row>
     <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="F58" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>80</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J58" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="J58" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B59" s="2">
         <v>3.2</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J59" s="6" t="s">
-        <v>19</v>
+      <c r="J59" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="E60" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>61</v>
@@ -4346,25 +4344,25 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>80</v>
@@ -4372,34 +4370,34 @@
       <c r="I61" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J61" s="6" t="s">
+      <c r="J61" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>18</v>
@@ -4410,28 +4408,28 @@
     </row>
     <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>44</v>
@@ -4442,28 +4440,28 @@
     </row>
     <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>18</v>
@@ -4474,28 +4472,28 @@
     </row>
     <row r="65" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="F65" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>306</v>
-      </c>
       <c r="H65" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>44</v>
@@ -4506,28 +4504,28 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B66" s="2">
         <v>5.0999999999999996</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>44</v>
@@ -4538,31 +4536,31 @@
     </row>
     <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>62</v>
@@ -4570,25 +4568,25 @@
     </row>
     <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="E68" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>80</v>
@@ -4596,31 +4594,31 @@
       <c r="I68" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J68" s="6" t="s">
+      <c r="J68" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>61</v>
@@ -4634,28 +4632,28 @@
     </row>
     <row r="70" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B70" s="2">
         <v>6.1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>18</v>
@@ -4666,28 +4664,28 @@
     </row>
     <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B71" s="2">
         <v>6.1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>44</v>
@@ -4698,25 +4696,25 @@
     </row>
     <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B72" s="2">
         <v>6.1</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>61</v>
@@ -4730,28 +4728,28 @@
     </row>
     <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B73" s="2">
         <v>6.1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D73" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>18</v>
@@ -4762,31 +4760,31 @@
     </row>
     <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B74" s="2">
         <v>6.2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>348</v>
-      </c>
       <c r="I74" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>27</v>
@@ -4794,57 +4792,57 @@
     </row>
     <row r="75" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>353</v>
+        <v>618</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J75" s="7" t="s">
-        <v>27</v>
+      <c r="J75" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>61</v>
@@ -4858,28 +4856,28 @@
     </row>
     <row r="77" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>18</v>
@@ -4890,25 +4888,25 @@
     </row>
     <row r="78" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>365</v>
+        <v>619</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>70</v>
@@ -4916,31 +4914,31 @@
       <c r="I78" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J78" s="7" t="s">
-        <v>27</v>
+      <c r="J78" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>54</v>
@@ -4954,25 +4952,25 @@
     </row>
     <row r="80" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>61</v>
@@ -4986,31 +4984,31 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>27</v>
@@ -5018,25 +5016,25 @@
     </row>
     <row r="82" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>54</v>
@@ -5050,25 +5048,25 @@
     </row>
     <row r="83" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>54</v>
@@ -5082,162 +5080,162 @@
     </row>
     <row r="84" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B84" s="2">
         <v>3.3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B85" s="2">
         <v>3.7</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>393</v>
-      </c>
       <c r="E85" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B86" s="2">
         <v>4.0999999999999996</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B87" s="2">
         <v>1.3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B88" s="2">
         <v>6.2</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -5267,22 +5265,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -5290,361 +5288,361 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E2" s="10">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E3" s="10">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E6" s="10">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E8" s="10">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>411</v>
+        <v>620</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>449</v>
+        <v>136</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E17" s="10">
         <v>1</v>
@@ -5653,53 +5651,53 @@
         <v>45</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E18" s="10">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E19" s="10">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -5728,19 +5726,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -5748,102 +5746,102 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B2" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B3" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B4" s="12">
         <v>2.2999999999999998</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5857,73 +5855,73 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -5931,79 +5929,79 @@
         <v>84</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>81</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B12" s="12">
         <v>3.5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B13" s="12">
         <v>3.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B14" s="12">
         <v>3.5</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6011,499 +6009,499 @@
         <v>93</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="12">
         <v>3.2</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B21" s="12">
         <v>3.2</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B22" s="12">
         <v>3.5</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B23" s="12">
         <v>3.5</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B24" s="12">
         <v>3.5</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B27" s="12">
         <v>3.2</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="12">
         <v>3.2</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B31" s="12">
         <v>3.7</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B32" s="12">
         <v>3.3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6534,16 +6532,16 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>9</v>
@@ -6554,19 +6552,19 @@
         <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6574,39 +6572,39 @@
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6614,79 +6612,79 @@
         <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -6694,79 +6692,79 @@
         <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6774,39 +6772,39 @@
         <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>567</v>
+        <v>621</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>568</v>
+        <v>622</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>449</v>
+        <v>561</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6814,59 +6812,59 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>556</v>
+        <v>623</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>572</v>
+        <v>624</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>573</v>
+        <v>625</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>556</v>
+        <v>626</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>574</v>
+        <v>627</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>449</v>
+        <v>564</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
